--- a/public/prices/price-promo.xlsx
+++ b/public/prices/price-promo.xlsx
@@ -76,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -84,25 +84,138 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E67"/>
+  <dimension ref="B2:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.66" customWidth="1" min="1" max="1"/>
@@ -498,868 +611,876 @@
           <t>Наименование товаров</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Акция</t>
         </is>
       </c>
+      <c r="D5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>(без учета НДС и НП)</t>
         </is>
       </c>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>DIKSON</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>RISTRUTTURANTE Комплекс реструктурирующий в ампулах 12х12 мл. 1127</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="14" t="n">
         <v>911</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Ср-во д/волос и кожи головы, защитный и тонизирующий эффект пчелиного молочка 10х10 мл. 0100 PAPPA REALE 1135</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="14" t="n">
         <v>641</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>LEVISSIME</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Краска для бровей и ресниц 1 черный 15 мл 1</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="14" t="n">
         <v>255</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Краска для бровей и ресниц 3/7 коричневый 15 мл 3-7</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="14" t="n">
         <v>255</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Краска для бровей и ресниц 6/71 натуральный коричневый 15 мл 6-71</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="14" t="n">
         <v>255</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Краска для бровей и ресниц 8/4 медный 15 мл 8-4</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="14" t="n">
         <v>255</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>LONDA</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>LIGHTPLEX №1 осветляющая пудра в коробке 2*500 мл 99240085775</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="14" t="n">
         <v>2999</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Блондоран препар. д/интенс. освет. волос 2х500г New  7 уровень осв. 647</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="14" t="n">
         <v>2450</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Масло VELVET OIL с аргановым маслом 100 мл 7543</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="14" t="n">
         <v>799</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Ср-во VELVET OIL с аргановым маслом 750мл 1252</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="14" t="n">
         <v>1930</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>ср-во ВОССТАНАВЛИВАЮЩЕЕ д/поврежденных волос 750 мл 4952/10569</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="14" t="n">
         <v>1450</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Стабилизатор д/сохранения цвета 1000 мл 4927/10562</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="14" t="n">
         <v>1450</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Шампунь FIBER INFUSION восстанавливающий с кератином 1000 мл. 5094</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="14" t="n">
         <v>1598.85</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Шампунь FIBER INFUSION восстанавливающий с кератином 250 мл. 5084</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="14" t="n">
         <v>594.15</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Шампунь VELVET OIL с аргановым маслом 1000 мл. 1266</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="14" t="n">
         <v>1598.85</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Шампунь VELVET OIL с аргановым маслом 250 мл. 1248</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="14" t="n">
         <v>521.05</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>шампунь д/глубокой очистки  1000 мл 4945/10600</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="14" t="n">
         <v>1371.05</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Шампунь д/объма 1000 мл 4943/10588</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="14" t="n">
         <v>1337.05</v>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Шампунь д/поврежденных волос 1000 мл 4959/10564</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="14" t="n">
         <v>1337.05</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Шампунь д/поврежденных волос 250 мл 4958/10565</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="14" t="n">
         <v>497.25</v>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Шампунь д/сохранения цвета и блеска 250 мл 4934/10558</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="14" t="n">
         <v>497.25</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Шампунь против перхоти 250 мл 4924/10573</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="14" t="n">
         <v>497.25</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Шампунь увлажняющий д/волос 1000 мл 4910/10582</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="14" t="n">
         <v>1337.05</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>MATRIX</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Total Results New</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="19" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Кондиционер Brass Off 300 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 2235400</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="14" t="n">
         <v>819</v>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Кондиционер High Amplify для объема 300 ml. 311656</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="14" t="n">
         <v>842.45</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Шамп. Brass Off 300 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 313760/2236000</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="14" t="n">
         <v>854.26</v>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Шамп. Color Obsessed So Silver 300 ml. (нейтрализует желтые подтона на волосах 8-11 уровней) 312459/1577700</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="14" t="n">
         <v>854.26</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Шамп. Food For Soft увлажнение с авокадо и гиалур. 300 ml. 305811</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="14" t="n">
         <v>854.26</v>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Шамп. Instacure Anti-Breakage против ломкости 300 ml. 308092/3824800</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="14" t="n">
         <v>854.26</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>OLLIN</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="12" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Крем - флюид 15 в 1 (Ollin Perfect Hair Leave-in Cream-Fluid) – 250 мл 773304</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="14" t="n">
         <v>330</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>SCHWARZKOPF</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="12" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>OSIS</t>
         </is>
       </c>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="19" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 300 мл. 1970454</t>
         </is>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="14" t="n">
         <v>807.5</v>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 500 мл. 1970621</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="14" t="n">
         <v>977.5</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>Лак д/волос №3 фикс. 4+ ЭСФ SESSION 300 мл. 1970645</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="14" t="n">
         <v>807.5</v>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>Спрей с бриллиантовым блеском Sparkler 300 мл. 1970641</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="14" t="n">
         <v>988.55</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Спрей с бриллиантовым блеском Sparkler 500 мл. 43669</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="14" t="n">
         <v>1138.15</v>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>Спрей текстурирующий Стайлинг Volume Up 300 мл 1970916</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="14" t="n">
         <v>833</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Спрей термозащитный Super Shield 300мл 4045787936612</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="14" t="n">
         <v>833</v>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>SILHOUETTE</t>
         </is>
       </c>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="19" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>Безупречный спрей ультрасильной фиксации 200 мл 2646468</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="14" t="n">
         <v>767</v>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>Гель д/волос сверхсильной фиксации 250мл 2147236</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="14" t="n">
         <v>660</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>Лак для волос ультрасильной фиксации 500мл 1937472/1581304</t>
         </is>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="14" t="n">
         <v>820</v>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>Красители и специальные прдукты IGORA</t>
         </is>
       </c>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="19" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>NS Лосьон д/химической завивки нормальных волос №1 1000мл 1969343</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="14" t="n">
         <v>2103.75</v>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>NS Лосьон д/химической завивки окрашенных волос №2 1000мл 1969347</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="14" t="n">
         <v>2103.75</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>NS Нейтрализатор для стойкого результата 1000мл 1969345</t>
         </is>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="14" t="n">
         <v>2103.75</v>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>Professionnelle Лак СФ  (Венгрия) 500 мл. 8701</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="14" t="n">
         <v>830</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>Игора Варио Блонд PLUS (БЕЛАЯ БАНКА 7+) 450гр 2242113</t>
         </is>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="14" t="n">
         <v>1650</v>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>Игора Варио Блонд SUPER PLUS (СИНЯЯ БАНКА 8+) 450 (НОВЫЙ ДИЗАЙН!) 2242115new</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="14" t="n">
         <v>1650</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>TIGI</t>
         </is>
       </c>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="12" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>Крем дефинирующий для вьющихся волос,Curls Rock Amplifier, 113 МЛ 3215-2152-68652722</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="14" t="n">
         <v>920</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>WELLA</t>
         </is>
       </c>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="12" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>EIMI</t>
         </is>
       </c>
-      <c r="C66" s="9" t="n"/>
-      <c r="D66" s="9" t="n"/>
-      <c r="E66" s="9" t="n"/>
+      <c r="C66" s="17" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="19" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>лак перфоманс ЭСФ 500 мл 11198/4138</t>
         </is>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="14" t="n">
         <v>759</v>
       </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/prices/price-promo.xlsx
+++ b/public/prices/price-promo.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; руб.&quot;"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -76,7 +78,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -88,81 +90,113 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -174,48 +208,56 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,906 +623,889 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E68"/>
+  <dimension ref="B1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.66" customWidth="1" min="1" max="1"/>
+    <col width="2.71" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="15.33" customWidth="1" min="3" max="3"/>
+    <col width="15.29" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10.33" customWidth="1" min="5" max="5"/>
+    <col width="10.29" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1" ht="26.25" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Акции</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Прайс-лист. Акции</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>24 Августа 2026 г.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1"/>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Наименование товаров</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Акция</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>1. База</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>(без учета НДС и НП)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>(без учета НДС и НП)</t>
-        </is>
-      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>DIKSON</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
       <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>DIKSON</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="12" t="n"/>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>RISTRUTTURANTE Комплекс реструктурирующий в ампулах 12х12 мл. 1127</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>911</v>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>RISTRUTTURANTE Комплекс реструктурирующий в ампулах 12х12 мл. 1127</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>911</v>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Ср-во д/волос и кожи головы, защитный и тонизирующий эффект пчелиного молочка 10х10 мл. 0100 PAPPA REALE 1135</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>641</v>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Ср-во д/волос и кожи головы, защитный и тонизирующий эффект пчелиного молочка 10х10 мл. 0100 PAPPA REALE 1135</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>641</v>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>LEVISSIME</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>LEVISSIME</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="12" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Краска для бровей и ресниц 1 черный 15 мл 1</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Краска для бровей и ресниц 1 черный 15 мл 1</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Краска для бровей и ресниц 3/7 коричневый 15 мл 3-7</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Краска для бровей и ресниц 3/7 коричневый 15 мл 3-7</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Краска для бровей и ресниц 6/71 натуральный коричневый 15 мл 6-71</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Краска для бровей и ресниц 6/71 натуральный коричневый 15 мл 6-71</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Краска для бровей и ресниц 8/4 медный 15 мл 8-4</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Краска для бровей и ресниц 8/4 медный 15 мл 8-4</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>255</v>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>LONDA</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>LONDA</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>LIGHTPLEX №1 осветляющая пудра в коробке 2*500 мл 99240085775</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>2999</v>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>LIGHTPLEX №1 осветляющая пудра в коробке 2*500 мл 99240085775</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>2999</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Блондоран препар. д/интенс. освет. волос 2х500г New  7 уровень осв. 647</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Блондоран препар. д/интенс. освет. волос 2х500г New  7 уровень осв. 647</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>2450</v>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Масло VELVET OIL с аргановым маслом 100 мл 7543</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>799</v>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Масло VELVET OIL с аргановым маслом 100 мл 7543</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>799</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Ср-во VELVET OIL с аргановым маслом 750мл 1252</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Ср-во VELVET OIL с аргановым маслом 750мл 1252</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>1930</v>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>ср-во ВОССТАНАВЛИВАЮЩЕЕ д/поврежденных волос 750 мл 4952/10569</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>ср-во ВОССТАНАВЛИВАЮЩЕЕ д/поврежденных волос 750 мл 4952/10569</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Стабилизатор д/сохранения цвета 1000 мл 4927/10562</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
         <v>1450</v>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Стабилизатор д/сохранения цвета 1000 мл 4927/10562</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1450</v>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 1000 мл. 5094</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>1598.85</v>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 1000 мл. 5094</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 250 мл. 5084</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>594.15</v>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь VELVET OIL с аргановым маслом 1000 мл. 1266</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
         <v>1598.85</v>
       </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 250 мл. 5084</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>594.15</v>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь VELVET OIL с аргановым маслом 1000 мл. 1266</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1598.85</v>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь VELVET OIL с аргановым маслом 250 мл. 1248</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>521.05</v>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь VELVET OIL с аргановым маслом 250 мл. 1248</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>521.05</v>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>шампунь д/глубокой очистки  1000 мл 4945/10600</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1371.05</v>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>шампунь д/глубокой очистки  1000 мл 4945/10600</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1371.05</v>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь д/объма 1000 мл 4943/10588</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>1337.05</v>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь д/объма 1000 мл 4943/10588</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь д/поврежденных волос 1000 мл 4959/10564</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
         <v>1337.05</v>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь д/поврежденных волос 1000 мл 4959/10564</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь д/поврежденных волос 250 мл 4958/10565</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>497.25</v>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь д/сохранения цвета и блеска 250 мл 4934/10558</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>497.25</v>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь против перхоти 250 мл 4924/10573</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>497.25</v>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Шампунь увлажняющий д/волос 1000 мл 4910/10582</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
         <v>1337.05</v>
       </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь д/поврежденных волос 250 мл 4958/10565</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>497.25</v>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь д/сохранения цвета и блеска 250 мл 4934/10558</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>497.25</v>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь против перхоти 250 мл 4924/10573</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>497.25</v>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Шампунь увлажняющий д/волос 1000 мл 4910/10582</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1337.05</v>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>MATRIX</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="12" t="n"/>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Total Results New</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>Total Results New</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="n"/>
-      <c r="D34" s="18" t="n"/>
-      <c r="E34" s="19" t="n"/>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Кондиционер Brass Off 300 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 2235400</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>819</v>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>Кондиционер Brass Off 300 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 2235400</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>819</v>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Кондиционер High Amplify для объема 300 ml. 311656</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>842.45</v>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Кондиционер High Amplify для объема 300 ml. 311656</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>842.45</v>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Шамп. Brass Off 300 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 313760/2236000</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>854.26</v>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Шамп. Brass Off 300 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 313760/2236000</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Шамп. Color Obsessed So Silver 300 ml. (нейтрализует желтые подтона на волосах 8-11 уровней) 312459/1577700</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
         <v>854.26</v>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Шамп. Color Obsessed So Silver 300 ml. (нейтрализует желтые подтона на волосах 8-11 уровней) 312459/1577700</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Шамп. Food For Soft увлажнение с авокадо и гиалур. 300 ml. 305811</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
         <v>854.26</v>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Шамп. Food For Soft увлажнение с авокадо и гиалур. 300 ml. 305811</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Шамп. Instacure Anti-Breakage против ломкости 300 ml. 308092/3824800</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
         <v>854.26</v>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Шамп. Instacure Anti-Breakage против ломкости 300 ml. 308092/3824800</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>854.26</v>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>OLLIN</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>OLLIN</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="12" t="n"/>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Крем - флюид 15 в 1 (Ollin Perfect Hair Leave-in Cream-Fluid) – 250 мл 773304</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>330</v>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>Крем - флюид 15 в 1 (Ollin Perfect Hair Leave-in Cream-Fluid) – 250 мл 773304</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>330</v>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>SCHWARZKOPF</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>SCHWARZKOPF</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="12" t="n"/>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>OSIS</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>OSIS</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="19" t="n"/>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 300 мл. 1970454</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>807.5</v>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 300 мл. 1970454</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 500 мл. 1970621</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>977.5</v>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Лак д/волос №3 фикс. 4+ ЭСФ SESSION 300 мл. 1970645</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
         <v>807.5</v>
       </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 500 мл. 1970621</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>977.5</v>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Лак д/волос №3 фикс. 4+ ЭСФ SESSION 300 мл. 1970645</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
-        <v>807.5</v>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Спрей с бриллиантовым блеском Sparkler 300 мл. 1970641</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>988.55</v>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Спрей с бриллиантовым блеском Sparkler 300 мл. 1970641</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="n">
-        <v>988.55</v>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Спрей с бриллиантовым блеском Sparkler 500 мл. 43669</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>1138.15</v>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Спрей с бриллиантовым блеском Sparkler 500 мл. 43669</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>1138.15</v>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Спрей текстурирующий Стайлинг Volume Up 300 мл 1970916</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>833</v>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>Спрей текстурирующий Стайлинг Volume Up 300 мл 1970916</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Спрей термозащитный Super Shield 300мл 4045787936612</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
         <v>833</v>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>Спрей термозащитный Super Shield 300мл 4045787936612</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>833</v>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>SILHOUETTE</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="8" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>SILHOUETTE</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="19" t="n"/>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Безупречный спрей ультрасильной фиксации 200 мл 2646468</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>767</v>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>Безупречный спрей ультрасильной фиксации 200 мл 2646468</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n">
-        <v>767</v>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Гель д/волос сверхсильной фиксации 250мл 2147236</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>660</v>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>Гель д/волос сверхсильной фиксации 250мл 2147236</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>660</v>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Лак для волос ультрасильной фиксации 500мл 1937472/1581304</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>820</v>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>Лак для волос ультрасильной фиксации 500мл 1937472/1581304</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n">
-        <v>820</v>
-      </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Красители и специальные прдукты IGORA</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>Красители и специальные прдукты IGORA</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="19" t="n"/>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>NS Лосьон д/химической завивки нормальных волос №1 1000мл 1969343</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>2103.75</v>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>NS Лосьон д/химической завивки нормальных волос №1 1000мл 1969343</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>NS Лосьон д/химической завивки окрашенных волос №2 1000мл 1969347</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="n">
         <v>2103.75</v>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>NS Лосьон д/химической завивки окрашенных волос №2 1000мл 1969347</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>NS Нейтрализатор для стойкого результата 1000мл 1969345</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="n">
         <v>2103.75</v>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>NS Нейтрализатор для стойкого результата 1000мл 1969345</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>2103.75</v>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Professionnelle Лак СФ  (Венгрия) 500 мл. 8701</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="n">
+        <v>830</v>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>Professionnelle Лак СФ  (Венгрия) 500 мл. 8701</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n">
-        <v>830</v>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Игора Варио Блонд PLUS (БЕЛАЯ БАНКА 7+) 450гр 2242113</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>Игора Варио Блонд PLUS (БЕЛАЯ БАНКА 7+) 450гр 2242113</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Игора Варио Блонд SUPER PLUS (СИНЯЯ БАНКА 8+) 450 (НОВЫЙ ДИЗАЙН!) 2242115new</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="n">
         <v>1650</v>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>Игора Варио Блонд SUPER PLUS (СИНЯЯ БАНКА 8+) 450 (НОВЫЙ ДИЗАЙН!) 2242115new</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>TIGI</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="8" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>TIGI</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="n"/>
-      <c r="D63" s="11" t="n"/>
-      <c r="E63" s="12" t="n"/>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Крем дефинирующий для вьющихся волос,Curls Rock Amplifier, 113 МЛ 3215-2152-68652722</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="n">
+        <v>920</v>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>Крем дефинирующий для вьющихся волос,Curls Rock Amplifier, 113 МЛ 3215-2152-68652722</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>920</v>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>WELLA</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="8" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>WELLA</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="11" t="n"/>
-      <c r="E65" s="12" t="n"/>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>EIMI</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="n"/>
+      <c r="D65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>EIMI</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="n"/>
-      <c r="D66" s="18" t="n"/>
-      <c r="E66" s="19" t="n"/>
-    </row>
-    <row r="67">
-      <c r="B67" s="13" t="inlineStr">
-        <is>
           <t>лак перфоманс ЭСФ 500 мл 11198/4138</t>
         </is>
       </c>
-      <c r="C67" s="14" t="n">
+      <c r="C66" s="17" t="n">
         <v>759</v>
       </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
